--- a/yudao-module-wms/yudao-module-wms-biz/src/main/resources/templates/logic-move-import.xlsx
+++ b/yudao-module-wms/yudao-module-wms-biz/src/main/resources/templates/logic-move-import.xlsx
@@ -27,9 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t>产品代码</t>
+  </si>
+  <si>
+    <t>仓库ID</t>
   </si>
   <si>
     <t>调出公司</t>
@@ -47,16 +50,10 @@
     <t>移动数量</t>
   </si>
   <si>
-    <t>RS-RO600</t>
+    <t>W06F3058C-M</t>
   </si>
   <si>
-    <t>DT205401WO</t>
-  </si>
-  <si>
-    <t>TTC1607AGW</t>
-  </si>
-  <si>
-    <t>W11F4126L</t>
+    <t>宁波索迈</t>
   </si>
 </sst>
 </file>
@@ -69,11 +66,11 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -84,14 +81,20 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <sz val="10.5"/>
+      <color rgb="FF606266"/>
+      <name val="Noto Sans SC"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -99,7 +102,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -107,14 +110,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -122,7 +125,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -130,7 +133,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -138,7 +141,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -146,7 +149,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -154,14 +157,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -169,7 +172,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -177,7 +180,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -185,14 +188,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -200,42 +203,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -563,213 +566,216 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常規" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="貨幣" xfId="2" builtinId="4"/>
     <cellStyle name="百分比" xfId="3" builtinId="5"/>
     <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="貨幣[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超鏈接" xfId="6" builtinId="8"/>
+    <cellStyle name="已訪問的超鏈接" xfId="7" builtinId="9"/>
+    <cellStyle name="註釋" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文字" xfId="9" builtinId="11"/>
+    <cellStyle name="標題" xfId="10" builtinId="15"/>
+    <cellStyle name="解釋性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="標題 1" xfId="12" builtinId="16"/>
+    <cellStyle name="標題 2" xfId="13" builtinId="17"/>
+    <cellStyle name="標題 3" xfId="14" builtinId="18"/>
+    <cellStyle name="標題 4" xfId="15" builtinId="19"/>
+    <cellStyle name="輸入" xfId="16" builtinId="20"/>
+    <cellStyle name="輸出" xfId="17" builtinId="21"/>
+    <cellStyle name="計算" xfId="18" builtinId="22"/>
+    <cellStyle name="檢查儲存格" xfId="19" builtinId="23"/>
+    <cellStyle name="鏈接儲存格" xfId="20" builtinId="24"/>
+    <cellStyle name="匯總" xfId="21" builtinId="25"/>
     <cellStyle name="好" xfId="22" builtinId="26"/>
     <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="適中" xfId="24" builtinId="28"/>
+    <cellStyle name="強調文字顏色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 強調文字顏色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 強調文字顏色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 強調文字顏色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="強調文字顏色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 強調文字顏色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 強調文字顏色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 強調文字顏色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="強調文字顏色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 強調文字顏色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 強調文字顏色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 強調文字顏色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="強調文字顏色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 強調文字顏色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 強調文字顏色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 強調文字顏色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="強調文字顏色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 強調文字顏色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 強調文字顏色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 強調文字顏色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="強調文字顏色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 強調文字顏色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 強調文字顏色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 強調文字顏色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -1252,18 +1258,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="16.5454545454545" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="12.1818181818182" customWidth="1"/>
-    <col min="6" max="6" width="11.5454545454545" customWidth="1"/>
+    <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="16.5454545454545" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="12.1818181818182" customWidth="1"/>
+    <col min="7" max="7" width="11.5454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35" spans="1:6">
+    <row r="1" ht="17.5" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1282,46 +1288,59 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" ht="14.5" spans="1:6">
-      <c r="A2" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
     </row>
-    <row r="3" ht="14.5" spans="1:6">
-      <c r="A3" s="2" t="s">
+    <row r="2" ht="17" spans="1:7">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" ht="14.5" spans="1:6">
-      <c r="A4" s="2" t="s">
+      <c r="B2">
+        <v>43</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="3">
+        <v>10</v>
+      </c>
     </row>
-    <row r="5" ht="14.5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+    <row r="3" spans="1:7">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
